--- a/diseases/d128/2020-2025.xlsx
+++ b/diseases/d128/2020-2025.xlsx
@@ -1209,9 +1209,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1605,9 +1602,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2789,9 +2783,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3825,9 +3816,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4861,9 +4849,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -6193,9 +6178,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -7377,9 +7359,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -8413,9 +8392,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -9745,9 +9721,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -11225,9 +11198,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -12557,9 +12527,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -13889,9 +13856,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -15073,9 +15037,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -16257,9 +16218,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -16801,9 +16759,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -17837,9 +17792,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -18873,9 +18825,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -19909,9 +19858,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -21093,9 +21039,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -22129,9 +22072,6 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
@@ -23461,9 +23401,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -24793,9 +24730,6 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0</v>
       </c>
@@ -26273,9 +26207,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -27457,9 +27388,6 @@
       <c r="O181" t="n">
         <v>0</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0</v>
       </c>
@@ -29085,9 +29013,6 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0</v>
       </c>
@@ -30417,9 +30342,6 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0</v>
       </c>
@@ -32045,9 +31967,6 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0</v>
       </c>
@@ -33081,9 +33000,6 @@
       <c r="O219" t="n">
         <v>0</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0</v>
       </c>
@@ -34265,9 +34181,6 @@
       <c r="O227" t="n">
         <v>0</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0</v>
       </c>
@@ -35597,9 +35510,6 @@
       <c r="O236" t="n">
         <v>0</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0</v>
       </c>
@@ -36633,9 +36543,6 @@
       <c r="O243" t="n">
         <v>0</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0</v>
       </c>
@@ -37817,9 +37724,6 @@
       <c r="O251" t="n">
         <v>0</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0</v>
       </c>
@@ -39001,9 +38905,6 @@
       <c r="O259" t="n">
         <v>0</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0</v>
       </c>
@@ -40185,9 +40086,6 @@
       <c r="O267" t="n">
         <v>0</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0</v>
       </c>
@@ -41517,9 +41415,6 @@
       <c r="O276" t="n">
         <v>0</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0</v>
       </c>
@@ -43145,9 +43040,6 @@
       <c r="O287" t="n">
         <v>0</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>0</v>
       </c>
@@ -44477,9 +44369,6 @@
       <c r="O296" t="n">
         <v>0</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="R296" t="n">
         <v>0</v>
       </c>
@@ -45513,9 +45402,6 @@
       <c r="O303" t="n">
         <v>0</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0</v>
       </c>
@@ -46845,9 +46731,6 @@
       <c r="O312" t="n">
         <v>0</v>
       </c>
-      <c r="Q312" t="n">
-        <v>0</v>
-      </c>
       <c r="R312" t="n">
         <v>0</v>
       </c>
@@ -47881,9 +47764,6 @@
       <c r="O319" t="n">
         <v>0</v>
       </c>
-      <c r="Q319" t="n">
-        <v>0</v>
-      </c>
       <c r="R319" t="n">
         <v>0</v>
       </c>
@@ -48917,9 +48797,6 @@
       <c r="O326" t="n">
         <v>0</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>0</v>
       </c>
@@ -50101,9 +49978,6 @@
       <c r="O334" t="n">
         <v>0</v>
       </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
       <c r="R334" t="n">
         <v>0</v>
       </c>
@@ -51137,9 +51011,6 @@
       <c r="O341" t="n">
         <v>0</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>0</v>
       </c>
@@ -52173,9 +52044,6 @@
       <c r="O348" t="n">
         <v>0</v>
       </c>
-      <c r="Q348" t="n">
-        <v>0</v>
-      </c>
       <c r="R348" t="n">
         <v>0</v>
       </c>
@@ -53357,9 +53225,6 @@
       <c r="O356" t="n">
         <v>0</v>
       </c>
-      <c r="Q356" t="n">
-        <v>0</v>
-      </c>
       <c r="R356" t="n">
         <v>0</v>
       </c>
@@ -54393,9 +54258,6 @@
       <c r="O363" t="n">
         <v>0</v>
       </c>
-      <c r="Q363" t="n">
-        <v>0</v>
-      </c>
       <c r="R363" t="n">
         <v>0</v>
       </c>
@@ -55577,9 +55439,6 @@
       <c r="O371" t="n">
         <v>0</v>
       </c>
-      <c r="Q371" t="n">
-        <v>0</v>
-      </c>
       <c r="R371" t="n">
         <v>0</v>
       </c>
@@ -56613,9 +56472,6 @@
       <c r="O378" t="n">
         <v>0</v>
       </c>
-      <c r="Q378" t="n">
-        <v>0</v>
-      </c>
       <c r="R378" t="n">
         <v>0</v>
       </c>
@@ -57649,9 +57505,6 @@
       <c r="O385" t="n">
         <v>0</v>
       </c>
-      <c r="Q385" t="n">
-        <v>0</v>
-      </c>
       <c r="R385" t="n">
         <v>0</v>
       </c>
@@ -58833,9 +58686,6 @@
       <c r="O393" t="n">
         <v>0</v>
       </c>
-      <c r="Q393" t="n">
-        <v>0</v>
-      </c>
       <c r="R393" t="n">
         <v>0</v>
       </c>
@@ -59721,9 +59571,6 @@
       <c r="O399" t="n">
         <v>1</v>
       </c>
-      <c r="Q399" t="n">
-        <v>0</v>
-      </c>
       <c r="R399" t="n">
         <v>0.01120827314023646</v>
       </c>
@@ -60017,9 +59864,6 @@
       <c r="O401" t="n">
         <v>0</v>
       </c>
-      <c r="Q401" t="n">
-        <v>0</v>
-      </c>
       <c r="R401" t="n">
         <v>0</v>
       </c>
@@ -61053,9 +60897,6 @@
       <c r="O408" t="n">
         <v>0</v>
       </c>
-      <c r="Q408" t="n">
-        <v>0</v>
-      </c>
       <c r="R408" t="n">
         <v>0</v>
       </c>
@@ -62237,9 +62078,6 @@
       <c r="O416" t="n">
         <v>0</v>
       </c>
-      <c r="Q416" t="n">
-        <v>0</v>
-      </c>
       <c r="R416" t="n">
         <v>0</v>
       </c>
@@ -63273,9 +63111,6 @@
       <c r="O423" t="n">
         <v>0</v>
       </c>
-      <c r="Q423" t="n">
-        <v>0</v>
-      </c>
       <c r="R423" t="n">
         <v>0</v>
       </c>
@@ -64309,9 +64144,6 @@
       <c r="O430" t="n">
         <v>0</v>
       </c>
-      <c r="Q430" t="n">
-        <v>0</v>
-      </c>
       <c r="R430" t="n">
         <v>0</v>
       </c>
@@ -65493,9 +65325,6 @@
       <c r="O438" t="n">
         <v>0</v>
       </c>
-      <c r="Q438" t="n">
-        <v>0</v>
-      </c>
       <c r="R438" t="n">
         <v>0</v>
       </c>
@@ -66529,9 +66358,6 @@
       <c r="O445" t="n">
         <v>0</v>
       </c>
-      <c r="Q445" t="n">
-        <v>0</v>
-      </c>
       <c r="R445" t="n">
         <v>0</v>
       </c>
@@ -67565,9 +67391,6 @@
       <c r="O452" t="n">
         <v>0</v>
       </c>
-      <c r="Q452" t="n">
-        <v>0</v>
-      </c>
       <c r="R452" t="n">
         <v>0</v>
       </c>
@@ -68749,9 +68572,6 @@
       <c r="O460" t="n">
         <v>0</v>
       </c>
-      <c r="Q460" t="n">
-        <v>0</v>
-      </c>
       <c r="R460" t="n">
         <v>0</v>
       </c>
@@ -69785,9 +69605,6 @@
       <c r="O467" t="n">
         <v>0</v>
       </c>
-      <c r="Q467" t="n">
-        <v>0</v>
-      </c>
       <c r="R467" t="n">
         <v>0</v>
       </c>
@@ -70969,9 +70786,6 @@
       <c r="O475" t="n">
         <v>0</v>
       </c>
-      <c r="Q475" t="n">
-        <v>0</v>
-      </c>
       <c r="R475" t="n">
         <v>0</v>
       </c>
@@ -72005,9 +71819,6 @@
       <c r="O482" t="n">
         <v>0</v>
       </c>
-      <c r="Q482" t="n">
-        <v>0</v>
-      </c>
       <c r="R482" t="n">
         <v>0</v>
       </c>
@@ -72893,9 +72704,6 @@
       <c r="O488" t="n">
         <v>1</v>
       </c>
-      <c r="Q488" t="n">
-        <v>0</v>
-      </c>
       <c r="R488" t="n">
         <v>0.01115149501123931</v>
       </c>
@@ -73189,9 +72997,6 @@
       <c r="O490" t="n">
         <v>0</v>
       </c>
-      <c r="Q490" t="n">
-        <v>0</v>
-      </c>
       <c r="R490" t="n">
         <v>0</v>
       </c>
@@ -74373,9 +74178,6 @@
       <c r="O498" t="n">
         <v>0</v>
       </c>
-      <c r="Q498" t="n">
-        <v>0</v>
-      </c>
       <c r="R498" t="n">
         <v>0</v>
       </c>
@@ -75409,9 +75211,6 @@
       <c r="O505" t="n">
         <v>0</v>
       </c>
-      <c r="Q505" t="n">
-        <v>0</v>
-      </c>
       <c r="R505" t="n">
         <v>0</v>
       </c>
@@ -76445,9 +76244,6 @@
       <c r="O512" t="n">
         <v>0</v>
       </c>
-      <c r="Q512" t="n">
-        <v>0</v>
-      </c>
       <c r="R512" t="n">
         <v>0</v>
       </c>
@@ -77481,9 +77277,6 @@
       <c r="O519" t="n">
         <v>0</v>
       </c>
-      <c r="Q519" t="n">
-        <v>0</v>
-      </c>
       <c r="R519" t="n">
         <v>0</v>
       </c>
@@ -78665,9 +78458,6 @@
       <c r="O527" t="n">
         <v>0</v>
       </c>
-      <c r="Q527" t="n">
-        <v>0</v>
-      </c>
       <c r="R527" t="n">
         <v>0</v>
       </c>
@@ -79701,9 +79491,6 @@
       <c r="O534" t="n">
         <v>0</v>
       </c>
-      <c r="Q534" t="n">
-        <v>0</v>
-      </c>
       <c r="R534" t="n">
         <v>0</v>
       </c>
@@ -80885,9 +80672,6 @@
       <c r="O542" t="n">
         <v>0</v>
       </c>
-      <c r="Q542" t="n">
-        <v>0</v>
-      </c>
       <c r="R542" t="n">
         <v>0</v>
       </c>
@@ -81921,9 +81705,6 @@
       <c r="O549" t="n">
         <v>0</v>
       </c>
-      <c r="Q549" t="n">
-        <v>0</v>
-      </c>
       <c r="R549" t="n">
         <v>0</v>
       </c>
@@ -82957,9 +82738,6 @@
       <c r="O556" t="n">
         <v>0</v>
       </c>
-      <c r="Q556" t="n">
-        <v>0</v>
-      </c>
       <c r="R556" t="n">
         <v>0</v>
       </c>
@@ -84141,9 +83919,6 @@
       <c r="O564" t="n">
         <v>0</v>
       </c>
-      <c r="Q564" t="n">
-        <v>0</v>
-      </c>
       <c r="R564" t="n">
         <v>0</v>
       </c>
@@ -85175,9 +84950,6 @@
         <v>0</v>
       </c>
       <c r="O571" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q571" t="n">
         <v>0</v>
       </c>
       <c r="R571" t="n">
